--- a/artfynd/A 34396-2023 artfynd.xlsx
+++ b/artfynd/A 34396-2023 artfynd.xlsx
@@ -1089,6 +1089,16 @@
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anna Zeffer</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anna Zeffer</t>
+        </is>
+      </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">

--- a/artfynd/A 34396-2023 artfynd.xlsx
+++ b/artfynd/A 34396-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128916024</v>
+        <v>128916103</v>
       </c>
       <c r="B2" t="n">
-        <v>97709</v>
+        <v>97507</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220686</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128916103</v>
+        <v>128916024</v>
       </c>
       <c r="B3" t="n">
-        <v>97503</v>
+        <v>97713</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>220686</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,7 +892,7 @@
         <v>128916540</v>
       </c>
       <c r="B4" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128916877</v>
       </c>
       <c r="B5" t="n">
-        <v>95868</v>
+        <v>95872</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128915303</v>
       </c>
       <c r="B6" t="n">
-        <v>97709</v>
+        <v>97713</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>128915345</v>
       </c>
       <c r="B7" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>128915036</v>
       </c>
       <c r="B8" t="n">
-        <v>95868</v>
+        <v>95872</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 34396-2023 artfynd.xlsx
+++ b/artfynd/A 34396-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128916103</v>
+        <v>128916024</v>
       </c>
       <c r="B2" t="n">
-        <v>97507</v>
+        <v>97713</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>220686</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128916024</v>
+        <v>128916103</v>
       </c>
       <c r="B3" t="n">
-        <v>97713</v>
+        <v>97507</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220686</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 34396-2023 artfynd.xlsx
+++ b/artfynd/A 34396-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128916024</v>
+        <v>128916103</v>
       </c>
       <c r="B2" t="n">
-        <v>97713</v>
+        <v>97507</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220686</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128916103</v>
+        <v>128916024</v>
       </c>
       <c r="B3" t="n">
-        <v>97507</v>
+        <v>97713</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>220686</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 34396-2023 artfynd.xlsx
+++ b/artfynd/A 34396-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128916103</v>
       </c>
       <c r="B2" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128916024</v>
       </c>
       <c r="B3" t="n">
-        <v>97713</v>
+        <v>97720</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128916540</v>
       </c>
       <c r="B4" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128916877</v>
       </c>
       <c r="B5" t="n">
-        <v>95872</v>
+        <v>95879</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128915303</v>
       </c>
       <c r="B6" t="n">
-        <v>97713</v>
+        <v>97720</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>128915345</v>
       </c>
       <c r="B7" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>128915036</v>
       </c>
       <c r="B8" t="n">
-        <v>95872</v>
+        <v>95879</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 34396-2023 artfynd.xlsx
+++ b/artfynd/A 34396-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128916103</v>
+        <v>128916024</v>
       </c>
       <c r="B2" t="n">
-        <v>97522</v>
+        <v>97733</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>220686</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128916024</v>
+        <v>128916103</v>
       </c>
       <c r="B3" t="n">
-        <v>97728</v>
+        <v>97527</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220686</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,7 +892,7 @@
         <v>128916540</v>
       </c>
       <c r="B4" t="n">
-        <v>97522</v>
+        <v>97527</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128916877</v>
       </c>
       <c r="B5" t="n">
-        <v>95887</v>
+        <v>95892</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128915303</v>
       </c>
       <c r="B6" t="n">
-        <v>97728</v>
+        <v>97733</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>128915345</v>
       </c>
       <c r="B7" t="n">
-        <v>97522</v>
+        <v>97527</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>128915036</v>
       </c>
       <c r="B8" t="n">
-        <v>95887</v>
+        <v>95892</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,32 +1424,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129042905</v>
+        <v>129042968</v>
       </c>
       <c r="B9" t="n">
-        <v>97272</v>
+        <v>57720</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>330386</v>
+        <v>330366</v>
       </c>
       <c r="R9" t="n">
-        <v>6438993</v>
+        <v>6438992</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,32 +1531,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129042968</v>
+        <v>129045442</v>
       </c>
       <c r="B10" t="n">
-        <v>57720</v>
+        <v>8439</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>330366</v>
+        <v>330427</v>
       </c>
       <c r="R10" t="n">
-        <v>6438992</v>
+        <v>6438678</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,32 +1638,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129045442</v>
+        <v>129041729</v>
       </c>
       <c r="B11" t="n">
-        <v>8439</v>
+        <v>57720</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>330427</v>
+        <v>330471</v>
       </c>
       <c r="R11" t="n">
-        <v>6438678</v>
+        <v>6438961</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,32 +1745,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129041729</v>
+        <v>129044975</v>
       </c>
       <c r="B12" t="n">
-        <v>57720</v>
+        <v>97527</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>330471</v>
+        <v>330281</v>
       </c>
       <c r="R12" t="n">
-        <v>6438961</v>
+        <v>6438766</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1855,7 +1855,7 @@
         <v>129041254</v>
       </c>
       <c r="B13" t="n">
-        <v>97728</v>
+        <v>97733</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1959,48 +1959,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129044975</v>
+        <v>129043672</v>
       </c>
       <c r="B14" t="n">
-        <v>97522</v>
+        <v>57720</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Assleröd bränna, Assleröd bränna, Boh</t>
+          <t>Assleröd, Boh</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>330281</v>
+        <v>330384</v>
       </c>
       <c r="R14" t="n">
-        <v>6438766</v>
+        <v>6439117</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2054,60 +2059,60 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anna Zeffer</t>
+          <t>Mats Eriksson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anna Zeffer</t>
+          <t>Mats Eriksson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129043672</v>
+        <v>129043852</v>
       </c>
       <c r="B15" t="n">
-        <v>57720</v>
+        <v>95892</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Assleröd, Boh</t>
+          <t>Assleröd, Assleröd, Boh</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>330384</v>
+        <v>330381</v>
       </c>
       <c r="R15" t="n">
-        <v>6439117</v>
+        <v>6439100</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2136,7 +2141,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2146,12 +2151,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:20</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Hack</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2166,22 +2166,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Mats Eriksson</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Mats Eriksson</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129043852</v>
+        <v>129042872</v>
       </c>
       <c r="B16" t="n">
-        <v>95887</v>
+        <v>97527</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2189,37 +2189,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2810</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Assleröd, Assleröd, Boh</t>
+          <t>Assleröd, Boh</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>330381</v>
+        <v>330413</v>
       </c>
       <c r="R16" t="n">
-        <v>6439100</v>
+        <v>6438980</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2273,22 +2273,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Mats Eriksson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Mats Eriksson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129042872</v>
+        <v>129041317</v>
       </c>
       <c r="B17" t="n">
-        <v>97522</v>
+        <v>95892</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2296,37 +2296,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>2810</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Assleröd, Boh</t>
+          <t>Assleröd bränna, Assleröd bränna, Boh</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>330413</v>
+        <v>330509</v>
       </c>
       <c r="R17" t="n">
-        <v>6438980</v>
+        <v>6438703</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2380,22 +2380,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Mats Eriksson</t>
+          <t>Anna Zeffer</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Mats Eriksson</t>
+          <t>Anna Zeffer</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129041317</v>
+        <v>129045313</v>
       </c>
       <c r="B18" t="n">
-        <v>95887</v>
+        <v>95892</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2427,10 +2427,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>330509</v>
+        <v>330360</v>
       </c>
       <c r="R18" t="n">
-        <v>6438703</v>
+        <v>6438739</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2499,10 +2499,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129043878</v>
+        <v>129045237</v>
       </c>
       <c r="B19" t="n">
-        <v>97522</v>
+        <v>97733</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2510,37 +2510,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>220686</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Assleröd, Boh</t>
+          <t>Assleröd bränna, Assleröd bränna, Boh</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>330393</v>
+        <v>330360</v>
       </c>
       <c r="R19" t="n">
-        <v>6439061</v>
+        <v>6438739</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2579,7 +2579,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2594,22 +2594,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Mats Eriksson</t>
+          <t>Anna Zeffer</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Mats Eriksson</t>
+          <t>Anna Zeffer</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129045313</v>
+        <v>129128187</v>
       </c>
       <c r="B20" t="n">
-        <v>95887</v>
+        <v>97527</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2617,37 +2617,49 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2810</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Assleröd bränna, Assleröd bränna, Boh</t>
+          <t>Assleröd, Boh</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>330360</v>
+        <v>330393</v>
       </c>
       <c r="R20" t="n">
-        <v>6438739</v>
+        <v>6439061</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2674,27 +2686,18 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>13:49</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>13:49</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2710,113 +2713,6 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>129045237</v>
-      </c>
-      <c r="B21" t="n">
-        <v>97728</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>220686</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Kambräken</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Blechnum spicant</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(L.) Roth</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Assleröd bränna, Assleröd bränna, Boh</t>
-        </is>
-      </c>
-      <c r="Q21" t="n">
-        <v>330360</v>
-      </c>
-      <c r="R21" t="n">
-        <v>6438739</v>
-      </c>
-      <c r="S21" t="n">
-        <v>10</v>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>Lilla Edet</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Bohuslän</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>Västerlanda</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="AD21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="inlineStr"/>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>Anna Zeffer</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>Anna Zeffer</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34396-2023 artfynd.xlsx
+++ b/artfynd/A 34396-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128916024</v>
       </c>
       <c r="B2" t="n">
-        <v>97733</v>
+        <v>97736</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128916103</v>
       </c>
       <c r="B3" t="n">
-        <v>97527</v>
+        <v>97530</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128916540</v>
       </c>
       <c r="B4" t="n">
-        <v>97527</v>
+        <v>97530</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128916877</v>
       </c>
       <c r="B5" t="n">
-        <v>95892</v>
+        <v>95895</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128915303</v>
       </c>
       <c r="B6" t="n">
-        <v>97733</v>
+        <v>97736</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>128915345</v>
       </c>
       <c r="B7" t="n">
-        <v>97527</v>
+        <v>97530</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>128915036</v>
       </c>
       <c r="B8" t="n">
-        <v>95892</v>
+        <v>95895</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>129044975</v>
       </c>
       <c r="B12" t="n">
-        <v>97527</v>
+        <v>97530</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>129041254</v>
       </c>
       <c r="B13" t="n">
-        <v>97733</v>
+        <v>97736</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>129043852</v>
       </c>
       <c r="B15" t="n">
-        <v>95892</v>
+        <v>95895</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2178,10 +2178,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129042872</v>
+        <v>129041317</v>
       </c>
       <c r="B16" t="n">
-        <v>97527</v>
+        <v>95895</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2189,37 +2189,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>2810</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Assleröd, Boh</t>
+          <t>Assleröd bränna, Assleröd bränna, Boh</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>330413</v>
+        <v>330509</v>
       </c>
       <c r="R16" t="n">
-        <v>6438980</v>
+        <v>6438703</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2273,22 +2273,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Mats Eriksson</t>
+          <t>Anna Zeffer</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Mats Eriksson</t>
+          <t>Anna Zeffer</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129041317</v>
+        <v>129042872</v>
       </c>
       <c r="B17" t="n">
-        <v>95892</v>
+        <v>97530</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2296,37 +2296,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2810</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Assleröd bränna, Assleröd bränna, Boh</t>
+          <t>Assleröd, Boh</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>330509</v>
+        <v>330413</v>
       </c>
       <c r="R17" t="n">
-        <v>6438703</v>
+        <v>6438980</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2380,12 +2380,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anna Zeffer</t>
+          <t>Mats Eriksson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anna Zeffer</t>
+          <t>Mats Eriksson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2395,7 +2395,7 @@
         <v>129045313</v>
       </c>
       <c r="B18" t="n">
-        <v>95892</v>
+        <v>95895</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>129045237</v>
       </c>
       <c r="B19" t="n">
-        <v>97733</v>
+        <v>97736</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>129128187</v>
       </c>
       <c r="B20" t="n">
-        <v>97527</v>
+        <v>97530</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 34396-2023 artfynd.xlsx
+++ b/artfynd/A 34396-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128916024</v>
+        <v>128916103</v>
       </c>
       <c r="B2" t="n">
-        <v>97736</v>
+        <v>97530</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220686</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128916103</v>
+        <v>128916024</v>
       </c>
       <c r="B3" t="n">
-        <v>97530</v>
+        <v>97736</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>220686</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -2178,10 +2178,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129041317</v>
+        <v>129042872</v>
       </c>
       <c r="B16" t="n">
-        <v>95895</v>
+        <v>97530</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2189,37 +2189,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2810</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Assleröd bränna, Assleröd bränna, Boh</t>
+          <t>Assleröd, Boh</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>330509</v>
+        <v>330413</v>
       </c>
       <c r="R16" t="n">
-        <v>6438703</v>
+        <v>6438980</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2273,22 +2273,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anna Zeffer</t>
+          <t>Mats Eriksson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anna Zeffer</t>
+          <t>Mats Eriksson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129042872</v>
+        <v>129041317</v>
       </c>
       <c r="B17" t="n">
-        <v>97530</v>
+        <v>95895</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2296,37 +2296,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>2810</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Assleröd, Boh</t>
+          <t>Assleröd bränna, Assleröd bränna, Boh</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>330413</v>
+        <v>330509</v>
       </c>
       <c r="R17" t="n">
-        <v>6438980</v>
+        <v>6438703</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2380,12 +2380,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Mats Eriksson</t>
+          <t>Anna Zeffer</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Mats Eriksson</t>
+          <t>Anna Zeffer</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 34396-2023 artfynd.xlsx
+++ b/artfynd/A 34396-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128916103</v>
+        <v>128916024</v>
       </c>
       <c r="B2" t="n">
-        <v>97530</v>
+        <v>97736</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>220686</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128916024</v>
+        <v>128916103</v>
       </c>
       <c r="B3" t="n">
-        <v>97736</v>
+        <v>97530</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220686</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -2178,10 +2178,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129042872</v>
+        <v>129041317</v>
       </c>
       <c r="B16" t="n">
-        <v>97530</v>
+        <v>95895</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2189,37 +2189,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>2810</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Assleröd, Boh</t>
+          <t>Assleröd bränna, Assleröd bränna, Boh</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>330413</v>
+        <v>330509</v>
       </c>
       <c r="R16" t="n">
-        <v>6438980</v>
+        <v>6438703</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2273,22 +2273,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Mats Eriksson</t>
+          <t>Anna Zeffer</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Mats Eriksson</t>
+          <t>Anna Zeffer</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129041317</v>
+        <v>129042872</v>
       </c>
       <c r="B17" t="n">
-        <v>95895</v>
+        <v>97530</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2296,37 +2296,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2810</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Assleröd bränna, Assleröd bränna, Boh</t>
+          <t>Assleröd, Boh</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>330509</v>
+        <v>330413</v>
       </c>
       <c r="R17" t="n">
-        <v>6438703</v>
+        <v>6438980</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2380,12 +2380,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anna Zeffer</t>
+          <t>Mats Eriksson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anna Zeffer</t>
+          <t>Mats Eriksson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 34396-2023 artfynd.xlsx
+++ b/artfynd/A 34396-2023 artfynd.xlsx
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129044975</v>
+        <v>129041254</v>
       </c>
       <c r="B12" t="n">
-        <v>97530</v>
+        <v>97736</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,21 +1756,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>220686</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>330281</v>
+        <v>330526</v>
       </c>
       <c r="R12" t="n">
-        <v>6438766</v>
+        <v>6438666</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129041254</v>
+        <v>129044975</v>
       </c>
       <c r="B13" t="n">
-        <v>97736</v>
+        <v>97530</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220686</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>330526</v>
+        <v>330281</v>
       </c>
       <c r="R13" t="n">
-        <v>6438666</v>
+        <v>6438766</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 34396-2023 artfynd.xlsx
+++ b/artfynd/A 34396-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128916024</v>
       </c>
       <c r="B2" t="n">
-        <v>97736</v>
+        <v>97746</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128916103</v>
       </c>
       <c r="B3" t="n">
-        <v>97530</v>
+        <v>97540</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128916540</v>
       </c>
       <c r="B4" t="n">
-        <v>97530</v>
+        <v>97540</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128916877</v>
       </c>
       <c r="B5" t="n">
-        <v>95895</v>
+        <v>95905</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128915303</v>
       </c>
       <c r="B6" t="n">
-        <v>97736</v>
+        <v>97746</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>128915345</v>
       </c>
       <c r="B7" t="n">
-        <v>97530</v>
+        <v>97540</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>128915036</v>
       </c>
       <c r="B8" t="n">
-        <v>95895</v>
+        <v>95905</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>129042968</v>
       </c>
       <c r="B9" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>129041729</v>
       </c>
       <c r="B11" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>129041254</v>
       </c>
       <c r="B12" t="n">
-        <v>97736</v>
+        <v>97746</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>129044975</v>
       </c>
       <c r="B13" t="n">
-        <v>97530</v>
+        <v>97540</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>129043672</v>
       </c>
       <c r="B14" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>129043852</v>
       </c>
       <c r="B15" t="n">
-        <v>95895</v>
+        <v>95905</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>129041317</v>
       </c>
       <c r="B16" t="n">
-        <v>95895</v>
+        <v>95905</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>129042872</v>
       </c>
       <c r="B17" t="n">
-        <v>97530</v>
+        <v>97540</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>129045313</v>
       </c>
       <c r="B18" t="n">
-        <v>95895</v>
+        <v>95905</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>129045237</v>
       </c>
       <c r="B19" t="n">
-        <v>97736</v>
+        <v>97746</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>129128187</v>
       </c>
       <c r="B20" t="n">
-        <v>97530</v>
+        <v>97540</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 34396-2023 artfynd.xlsx
+++ b/artfynd/A 34396-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128916024</v>
+        <v>128916103</v>
       </c>
       <c r="B2" t="n">
-        <v>97746</v>
+        <v>97547</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220686</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128916103</v>
+        <v>128916024</v>
       </c>
       <c r="B3" t="n">
-        <v>97540</v>
+        <v>97753</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>220686</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,7 +892,7 @@
         <v>128916540</v>
       </c>
       <c r="B4" t="n">
-        <v>97540</v>
+        <v>97547</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128916877</v>
       </c>
       <c r="B5" t="n">
-        <v>95905</v>
+        <v>95912</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128915303</v>
       </c>
       <c r="B6" t="n">
-        <v>97746</v>
+        <v>97753</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>128915345</v>
       </c>
       <c r="B7" t="n">
-        <v>97540</v>
+        <v>97547</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>128915036</v>
       </c>
       <c r="B8" t="n">
-        <v>95905</v>
+        <v>95912</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>129041254</v>
       </c>
       <c r="B12" t="n">
-        <v>97746</v>
+        <v>97753</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>129044975</v>
       </c>
       <c r="B13" t="n">
-        <v>97540</v>
+        <v>97547</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>129043852</v>
       </c>
       <c r="B15" t="n">
-        <v>95905</v>
+        <v>95912</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>129041317</v>
       </c>
       <c r="B16" t="n">
-        <v>95905</v>
+        <v>95912</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>129042872</v>
       </c>
       <c r="B17" t="n">
-        <v>97540</v>
+        <v>97547</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>129045313</v>
       </c>
       <c r="B18" t="n">
-        <v>95905</v>
+        <v>95912</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>129045237</v>
       </c>
       <c r="B19" t="n">
-        <v>97746</v>
+        <v>97753</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>129128187</v>
       </c>
       <c r="B20" t="n">
-        <v>97540</v>
+        <v>97547</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 34396-2023 artfynd.xlsx
+++ b/artfynd/A 34396-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128916103</v>
+        <v>128916024</v>
       </c>
       <c r="B2" t="n">
-        <v>97547</v>
+        <v>97755</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>220686</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128916024</v>
+        <v>128916103</v>
       </c>
       <c r="B3" t="n">
-        <v>97753</v>
+        <v>97549</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220686</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,7 +892,7 @@
         <v>128916540</v>
       </c>
       <c r="B4" t="n">
-        <v>97547</v>
+        <v>97549</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128916877</v>
       </c>
       <c r="B5" t="n">
-        <v>95912</v>
+        <v>95914</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128915303</v>
       </c>
       <c r="B6" t="n">
-        <v>97753</v>
+        <v>97755</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>128915345</v>
       </c>
       <c r="B7" t="n">
-        <v>97547</v>
+        <v>97549</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>128915036</v>
       </c>
       <c r="B8" t="n">
-        <v>95912</v>
+        <v>95914</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>129042968</v>
       </c>
       <c r="B9" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>129041729</v>
       </c>
       <c r="B11" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>129041254</v>
       </c>
       <c r="B12" t="n">
-        <v>97753</v>
+        <v>97755</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>129044975</v>
       </c>
       <c r="B13" t="n">
-        <v>97547</v>
+        <v>97549</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>129043672</v>
       </c>
       <c r="B14" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>129043852</v>
       </c>
       <c r="B15" t="n">
-        <v>95912</v>
+        <v>95914</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>129041317</v>
       </c>
       <c r="B16" t="n">
-        <v>95912</v>
+        <v>95914</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>129042872</v>
       </c>
       <c r="B17" t="n">
-        <v>97547</v>
+        <v>97549</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>129045313</v>
       </c>
       <c r="B18" t="n">
-        <v>95912</v>
+        <v>95914</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>129045237</v>
       </c>
       <c r="B19" t="n">
-        <v>97753</v>
+        <v>97755</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>129128187</v>
       </c>
       <c r="B20" t="n">
-        <v>97547</v>
+        <v>97549</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 34396-2023 artfynd.xlsx
+++ b/artfynd/A 34396-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128916024</v>
       </c>
       <c r="B2" t="n">
-        <v>97755</v>
+        <v>97781</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128916103</v>
       </c>
       <c r="B3" t="n">
-        <v>97549</v>
+        <v>97575</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128916540</v>
       </c>
       <c r="B4" t="n">
-        <v>97549</v>
+        <v>97575</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128916877</v>
       </c>
       <c r="B5" t="n">
-        <v>95914</v>
+        <v>95940</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128915303</v>
       </c>
       <c r="B6" t="n">
-        <v>97755</v>
+        <v>97781</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>128915345</v>
       </c>
       <c r="B7" t="n">
-        <v>97549</v>
+        <v>97575</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>128915036</v>
       </c>
       <c r="B8" t="n">
-        <v>95914</v>
+        <v>95940</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129041254</v>
+        <v>129044975</v>
       </c>
       <c r="B12" t="n">
-        <v>97755</v>
+        <v>97575</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,21 +1756,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220686</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>330526</v>
+        <v>330281</v>
       </c>
       <c r="R12" t="n">
-        <v>6438666</v>
+        <v>6438766</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129044975</v>
+        <v>129041254</v>
       </c>
       <c r="B13" t="n">
-        <v>97549</v>
+        <v>97781</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>220686</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>330281</v>
+        <v>330526</v>
       </c>
       <c r="R13" t="n">
-        <v>6438766</v>
+        <v>6438666</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2074,7 +2074,7 @@
         <v>129043852</v>
       </c>
       <c r="B15" t="n">
-        <v>95914</v>
+        <v>95940</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>129041317</v>
       </c>
       <c r="B16" t="n">
-        <v>95914</v>
+        <v>95940</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>129042872</v>
       </c>
       <c r="B17" t="n">
-        <v>97549</v>
+        <v>97575</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>129045313</v>
       </c>
       <c r="B18" t="n">
-        <v>95914</v>
+        <v>95940</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>129045237</v>
       </c>
       <c r="B19" t="n">
-        <v>97755</v>
+        <v>97781</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>129128187</v>
       </c>
       <c r="B20" t="n">
-        <v>97549</v>
+        <v>97575</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 34396-2023 artfynd.xlsx
+++ b/artfynd/A 34396-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128916024</v>
+        <v>128916103</v>
       </c>
       <c r="B2" t="n">
-        <v>97781</v>
+        <v>97576</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220686</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128916103</v>
+        <v>128916024</v>
       </c>
       <c r="B3" t="n">
-        <v>97575</v>
+        <v>97782</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>220686</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,7 +892,7 @@
         <v>128916540</v>
       </c>
       <c r="B4" t="n">
-        <v>97575</v>
+        <v>97576</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128916877</v>
       </c>
       <c r="B5" t="n">
-        <v>95940</v>
+        <v>95941</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128915303</v>
       </c>
       <c r="B6" t="n">
-        <v>97781</v>
+        <v>97782</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>128915345</v>
       </c>
       <c r="B7" t="n">
-        <v>97575</v>
+        <v>97576</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>128915036</v>
       </c>
       <c r="B8" t="n">
-        <v>95940</v>
+        <v>95941</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129044975</v>
+        <v>129041254</v>
       </c>
       <c r="B12" t="n">
-        <v>97575</v>
+        <v>97782</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,21 +1756,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>220686</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>330281</v>
+        <v>330526</v>
       </c>
       <c r="R12" t="n">
-        <v>6438766</v>
+        <v>6438666</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129041254</v>
+        <v>129044975</v>
       </c>
       <c r="B13" t="n">
-        <v>97781</v>
+        <v>97576</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220686</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>330526</v>
+        <v>330281</v>
       </c>
       <c r="R13" t="n">
-        <v>6438666</v>
+        <v>6438766</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2074,7 +2074,7 @@
         <v>129043852</v>
       </c>
       <c r="B15" t="n">
-        <v>95940</v>
+        <v>95941</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>129041317</v>
       </c>
       <c r="B16" t="n">
-        <v>95940</v>
+        <v>95941</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>129042872</v>
       </c>
       <c r="B17" t="n">
-        <v>97575</v>
+        <v>97576</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>129045313</v>
       </c>
       <c r="B18" t="n">
-        <v>95940</v>
+        <v>95941</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>129045237</v>
       </c>
       <c r="B19" t="n">
-        <v>97781</v>
+        <v>97782</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>129128187</v>
       </c>
       <c r="B20" t="n">
-        <v>97575</v>
+        <v>97576</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 34396-2023 artfynd.xlsx
+++ b/artfynd/A 34396-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128916103</v>
       </c>
       <c r="B2" t="n">
-        <v>97576</v>
+        <v>97577</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128916024</v>
       </c>
       <c r="B3" t="n">
-        <v>97782</v>
+        <v>97783</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128916540</v>
       </c>
       <c r="B4" t="n">
-        <v>97576</v>
+        <v>97577</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128916877</v>
       </c>
       <c r="B5" t="n">
-        <v>95941</v>
+        <v>95942</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128915303</v>
       </c>
       <c r="B6" t="n">
-        <v>97782</v>
+        <v>97783</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>128915345</v>
       </c>
       <c r="B7" t="n">
-        <v>97576</v>
+        <v>97577</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>128915036</v>
       </c>
       <c r="B8" t="n">
-        <v>95941</v>
+        <v>95942</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129041254</v>
+        <v>129044975</v>
       </c>
       <c r="B12" t="n">
-        <v>97782</v>
+        <v>97577</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,21 +1756,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220686</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>330526</v>
+        <v>330281</v>
       </c>
       <c r="R12" t="n">
-        <v>6438666</v>
+        <v>6438766</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129044975</v>
+        <v>129041254</v>
       </c>
       <c r="B13" t="n">
-        <v>97576</v>
+        <v>97783</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>220686</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>330281</v>
+        <v>330526</v>
       </c>
       <c r="R13" t="n">
-        <v>6438766</v>
+        <v>6438666</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2074,7 +2074,7 @@
         <v>129043852</v>
       </c>
       <c r="B15" t="n">
-        <v>95941</v>
+        <v>95942</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2178,10 +2178,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129041317</v>
+        <v>129042872</v>
       </c>
       <c r="B16" t="n">
-        <v>95941</v>
+        <v>97577</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2189,37 +2189,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2810</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Assleröd bränna, Assleröd bränna, Boh</t>
+          <t>Assleröd, Boh</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>330509</v>
+        <v>330413</v>
       </c>
       <c r="R16" t="n">
-        <v>6438703</v>
+        <v>6438980</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2273,22 +2273,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anna Zeffer</t>
+          <t>Mats Eriksson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anna Zeffer</t>
+          <t>Mats Eriksson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129042872</v>
+        <v>129041317</v>
       </c>
       <c r="B17" t="n">
-        <v>97576</v>
+        <v>95942</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2296,37 +2296,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>2810</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Assleröd, Boh</t>
+          <t>Assleröd bränna, Assleröd bränna, Boh</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>330413</v>
+        <v>330509</v>
       </c>
       <c r="R17" t="n">
-        <v>6438980</v>
+        <v>6438703</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2380,12 +2380,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Mats Eriksson</t>
+          <t>Anna Zeffer</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Mats Eriksson</t>
+          <t>Anna Zeffer</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2395,7 +2395,7 @@
         <v>129045313</v>
       </c>
       <c r="B18" t="n">
-        <v>95941</v>
+        <v>95942</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>129045237</v>
       </c>
       <c r="B19" t="n">
-        <v>97782</v>
+        <v>97783</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>129128187</v>
       </c>
       <c r="B20" t="n">
-        <v>97576</v>
+        <v>97577</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 34396-2023 artfynd.xlsx
+++ b/artfynd/A 34396-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128916103</v>
       </c>
       <c r="B2" t="n">
-        <v>97577</v>
+        <v>97581</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128916024</v>
       </c>
       <c r="B3" t="n">
-        <v>97783</v>
+        <v>97787</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128916540</v>
       </c>
       <c r="B4" t="n">
-        <v>97577</v>
+        <v>97581</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128916877</v>
       </c>
       <c r="B5" t="n">
-        <v>95942</v>
+        <v>95946</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128915303</v>
       </c>
       <c r="B6" t="n">
-        <v>97783</v>
+        <v>97787</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>128915345</v>
       </c>
       <c r="B7" t="n">
-        <v>97577</v>
+        <v>97581</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>128915036</v>
       </c>
       <c r="B8" t="n">
-        <v>95942</v>
+        <v>95946</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>129044975</v>
       </c>
       <c r="B12" t="n">
-        <v>97577</v>
+        <v>97581</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>129041254</v>
       </c>
       <c r="B13" t="n">
-        <v>97783</v>
+        <v>97787</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>129043852</v>
       </c>
       <c r="B15" t="n">
-        <v>95942</v>
+        <v>95946</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2178,10 +2178,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129042872</v>
+        <v>129041317</v>
       </c>
       <c r="B16" t="n">
-        <v>97577</v>
+        <v>95946</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2189,37 +2189,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>2810</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Assleröd, Boh</t>
+          <t>Assleröd bränna, Assleröd bränna, Boh</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>330413</v>
+        <v>330509</v>
       </c>
       <c r="R16" t="n">
-        <v>6438980</v>
+        <v>6438703</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2273,22 +2273,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Mats Eriksson</t>
+          <t>Anna Zeffer</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Mats Eriksson</t>
+          <t>Anna Zeffer</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129041317</v>
+        <v>129042872</v>
       </c>
       <c r="B17" t="n">
-        <v>95942</v>
+        <v>97581</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2296,37 +2296,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2810</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Assleröd bränna, Assleröd bränna, Boh</t>
+          <t>Assleröd, Boh</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>330509</v>
+        <v>330413</v>
       </c>
       <c r="R17" t="n">
-        <v>6438703</v>
+        <v>6438980</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2380,12 +2380,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anna Zeffer</t>
+          <t>Mats Eriksson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anna Zeffer</t>
+          <t>Mats Eriksson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2395,7 +2395,7 @@
         <v>129045313</v>
       </c>
       <c r="B18" t="n">
-        <v>95942</v>
+        <v>95946</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>129045237</v>
       </c>
       <c r="B19" t="n">
-        <v>97783</v>
+        <v>97787</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>129128187</v>
       </c>
       <c r="B20" t="n">
-        <v>97577</v>
+        <v>97581</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 34396-2023 artfynd.xlsx
+++ b/artfynd/A 34396-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128916103</v>
       </c>
       <c r="B2" t="n">
-        <v>97581</v>
+        <v>97583</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128916024</v>
       </c>
       <c r="B3" t="n">
-        <v>97787</v>
+        <v>97789</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128916540</v>
       </c>
       <c r="B4" t="n">
-        <v>97581</v>
+        <v>97583</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128916877</v>
       </c>
       <c r="B5" t="n">
-        <v>95946</v>
+        <v>95948</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128915303</v>
       </c>
       <c r="B6" t="n">
-        <v>97787</v>
+        <v>97789</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>128915345</v>
       </c>
       <c r="B7" t="n">
-        <v>97581</v>
+        <v>97583</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>128915036</v>
       </c>
       <c r="B8" t="n">
-        <v>95946</v>
+        <v>95948</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129044975</v>
+        <v>129041254</v>
       </c>
       <c r="B12" t="n">
-        <v>97581</v>
+        <v>97789</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,21 +1756,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>220686</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>330281</v>
+        <v>330526</v>
       </c>
       <c r="R12" t="n">
-        <v>6438766</v>
+        <v>6438666</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129041254</v>
+        <v>129044975</v>
       </c>
       <c r="B13" t="n">
-        <v>97787</v>
+        <v>97583</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220686</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>330526</v>
+        <v>330281</v>
       </c>
       <c r="R13" t="n">
-        <v>6438666</v>
+        <v>6438766</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2074,7 +2074,7 @@
         <v>129043852</v>
       </c>
       <c r="B15" t="n">
-        <v>95946</v>
+        <v>95948</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>129041317</v>
       </c>
       <c r="B16" t="n">
-        <v>95946</v>
+        <v>95948</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>129042872</v>
       </c>
       <c r="B17" t="n">
-        <v>97581</v>
+        <v>97583</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>129045313</v>
       </c>
       <c r="B18" t="n">
-        <v>95946</v>
+        <v>95948</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>129045237</v>
       </c>
       <c r="B19" t="n">
-        <v>97787</v>
+        <v>97789</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>129128187</v>
       </c>
       <c r="B20" t="n">
-        <v>97581</v>
+        <v>97583</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 34396-2023 artfynd.xlsx
+++ b/artfynd/A 34396-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128916103</v>
       </c>
       <c r="B2" t="n">
-        <v>97583</v>
+        <v>97587</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128916024</v>
       </c>
       <c r="B3" t="n">
-        <v>97789</v>
+        <v>97793</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128916540</v>
       </c>
       <c r="B4" t="n">
-        <v>97583</v>
+        <v>97587</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128916877</v>
       </c>
       <c r="B5" t="n">
-        <v>95948</v>
+        <v>95952</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128915303</v>
       </c>
       <c r="B6" t="n">
-        <v>97789</v>
+        <v>97793</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>128915345</v>
       </c>
       <c r="B7" t="n">
-        <v>97583</v>
+        <v>97587</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>128915036</v>
       </c>
       <c r="B8" t="n">
-        <v>95948</v>
+        <v>95952</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>129041254</v>
       </c>
       <c r="B12" t="n">
-        <v>97789</v>
+        <v>97793</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>129044975</v>
       </c>
       <c r="B13" t="n">
-        <v>97583</v>
+        <v>97587</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>129043852</v>
       </c>
       <c r="B15" t="n">
-        <v>95948</v>
+        <v>95952</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>129041317</v>
       </c>
       <c r="B16" t="n">
-        <v>95948</v>
+        <v>95952</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>129042872</v>
       </c>
       <c r="B17" t="n">
-        <v>97583</v>
+        <v>97587</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>129045313</v>
       </c>
       <c r="B18" t="n">
-        <v>95948</v>
+        <v>95952</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>129045237</v>
       </c>
       <c r="B19" t="n">
-        <v>97789</v>
+        <v>97793</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>129128187</v>
       </c>
       <c r="B20" t="n">
-        <v>97583</v>
+        <v>97587</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 34396-2023 artfynd.xlsx
+++ b/artfynd/A 34396-2023 artfynd.xlsx
@@ -1748,7 +1748,7 @@
         <v>129041254</v>
       </c>
       <c r="B12" t="n">
-        <v>97793</v>
+        <v>97801</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>129044975</v>
       </c>
       <c r="B13" t="n">
-        <v>97587</v>
+        <v>97595</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>129043852</v>
       </c>
       <c r="B15" t="n">
-        <v>95952</v>
+        <v>95960</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2178,10 +2178,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129041317</v>
+        <v>129042872</v>
       </c>
       <c r="B16" t="n">
-        <v>95952</v>
+        <v>97595</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2189,37 +2189,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2810</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Assleröd bränna, Assleröd bränna, Boh</t>
+          <t>Assleröd, Boh</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>330509</v>
+        <v>330413</v>
       </c>
       <c r="R16" t="n">
-        <v>6438703</v>
+        <v>6438980</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2273,22 +2273,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anna Zeffer</t>
+          <t>Mats Eriksson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anna Zeffer</t>
+          <t>Mats Eriksson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129042872</v>
+        <v>129041317</v>
       </c>
       <c r="B17" t="n">
-        <v>97587</v>
+        <v>95960</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2296,37 +2296,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>2810</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Assleröd, Boh</t>
+          <t>Assleröd bränna, Assleröd bränna, Boh</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>330413</v>
+        <v>330509</v>
       </c>
       <c r="R17" t="n">
-        <v>6438980</v>
+        <v>6438703</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2380,12 +2380,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Mats Eriksson</t>
+          <t>Anna Zeffer</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Mats Eriksson</t>
+          <t>Anna Zeffer</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2395,7 +2395,7 @@
         <v>129045313</v>
       </c>
       <c r="B18" t="n">
-        <v>95952</v>
+        <v>95960</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>129045237</v>
       </c>
       <c r="B19" t="n">
-        <v>97793</v>
+        <v>97801</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>129128187</v>
       </c>
       <c r="B20" t="n">
-        <v>97587</v>
+        <v>97595</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 34396-2023 artfynd.xlsx
+++ b/artfynd/A 34396-2023 artfynd.xlsx
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129041254</v>
+        <v>129044975</v>
       </c>
       <c r="B12" t="n">
-        <v>97801</v>
+        <v>97595</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,21 +1756,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220686</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>330526</v>
+        <v>330281</v>
       </c>
       <c r="R12" t="n">
-        <v>6438666</v>
+        <v>6438766</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129044975</v>
+        <v>129041254</v>
       </c>
       <c r="B13" t="n">
-        <v>97595</v>
+        <v>97801</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>220686</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>330281</v>
+        <v>330526</v>
       </c>
       <c r="R13" t="n">
-        <v>6438766</v>
+        <v>6438666</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2178,10 +2178,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129042872</v>
+        <v>129041317</v>
       </c>
       <c r="B16" t="n">
-        <v>97595</v>
+        <v>95960</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2189,37 +2189,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>2810</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Assleröd, Boh</t>
+          <t>Assleröd bränna, Assleröd bränna, Boh</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>330413</v>
+        <v>330509</v>
       </c>
       <c r="R16" t="n">
-        <v>6438980</v>
+        <v>6438703</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2273,22 +2273,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Mats Eriksson</t>
+          <t>Anna Zeffer</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Mats Eriksson</t>
+          <t>Anna Zeffer</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129041317</v>
+        <v>129042872</v>
       </c>
       <c r="B17" t="n">
-        <v>95960</v>
+        <v>97595</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2296,37 +2296,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2810</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Assleröd bränna, Assleröd bränna, Boh</t>
+          <t>Assleröd, Boh</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>330509</v>
+        <v>330413</v>
       </c>
       <c r="R17" t="n">
-        <v>6438703</v>
+        <v>6438980</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2380,12 +2380,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anna Zeffer</t>
+          <t>Mats Eriksson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anna Zeffer</t>
+          <t>Mats Eriksson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 34396-2023 artfynd.xlsx
+++ b/artfynd/A 34396-2023 artfynd.xlsx
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129044975</v>
+        <v>129041254</v>
       </c>
       <c r="B12" t="n">
-        <v>97595</v>
+        <v>97804</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,21 +1756,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>220686</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>330281</v>
+        <v>330526</v>
       </c>
       <c r="R12" t="n">
-        <v>6438766</v>
+        <v>6438666</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129041254</v>
+        <v>129044975</v>
       </c>
       <c r="B13" t="n">
-        <v>97801</v>
+        <v>97598</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220686</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>330526</v>
+        <v>330281</v>
       </c>
       <c r="R13" t="n">
-        <v>6438666</v>
+        <v>6438766</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2074,7 +2074,7 @@
         <v>129043852</v>
       </c>
       <c r="B15" t="n">
-        <v>95960</v>
+        <v>95963</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>129041317</v>
       </c>
       <c r="B16" t="n">
-        <v>95960</v>
+        <v>95963</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>129042872</v>
       </c>
       <c r="B17" t="n">
-        <v>97595</v>
+        <v>97598</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>129045313</v>
       </c>
       <c r="B18" t="n">
-        <v>95960</v>
+        <v>95963</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>129045237</v>
       </c>
       <c r="B19" t="n">
-        <v>97801</v>
+        <v>97804</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>129128187</v>
       </c>
       <c r="B20" t="n">
-        <v>97595</v>
+        <v>97598</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 34396-2023 artfynd.xlsx
+++ b/artfynd/A 34396-2023 artfynd.xlsx
@@ -2178,10 +2178,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129041317</v>
+        <v>129042872</v>
       </c>
       <c r="B16" t="n">
-        <v>95963</v>
+        <v>97598</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2189,37 +2189,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2810</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Assleröd bränna, Assleröd bränna, Boh</t>
+          <t>Assleröd, Boh</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>330509</v>
+        <v>330413</v>
       </c>
       <c r="R16" t="n">
-        <v>6438703</v>
+        <v>6438980</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2273,22 +2273,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anna Zeffer</t>
+          <t>Mats Eriksson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anna Zeffer</t>
+          <t>Mats Eriksson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129042872</v>
+        <v>129041317</v>
       </c>
       <c r="B17" t="n">
-        <v>97598</v>
+        <v>95963</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2296,37 +2296,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>2810</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Assleröd, Boh</t>
+          <t>Assleröd bränna, Assleröd bränna, Boh</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>330413</v>
+        <v>330509</v>
       </c>
       <c r="R17" t="n">
-        <v>6438980</v>
+        <v>6438703</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2380,12 +2380,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Mats Eriksson</t>
+          <t>Anna Zeffer</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Mats Eriksson</t>
+          <t>Anna Zeffer</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 34396-2023 artfynd.xlsx
+++ b/artfynd/A 34396-2023 artfynd.xlsx
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129041254</v>
+        <v>129044975</v>
       </c>
       <c r="B12" t="n">
-        <v>97804</v>
+        <v>97598</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,21 +1756,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220686</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>330526</v>
+        <v>330281</v>
       </c>
       <c r="R12" t="n">
-        <v>6438666</v>
+        <v>6438766</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129044975</v>
+        <v>129041254</v>
       </c>
       <c r="B13" t="n">
-        <v>97598</v>
+        <v>97804</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>220686</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>330281</v>
+        <v>330526</v>
       </c>
       <c r="R13" t="n">
-        <v>6438766</v>
+        <v>6438666</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2178,10 +2178,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129042872</v>
+        <v>129041317</v>
       </c>
       <c r="B16" t="n">
-        <v>97598</v>
+        <v>95963</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2189,37 +2189,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>2810</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Assleröd, Boh</t>
+          <t>Assleröd bränna, Assleröd bränna, Boh</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>330413</v>
+        <v>330509</v>
       </c>
       <c r="R16" t="n">
-        <v>6438980</v>
+        <v>6438703</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2273,22 +2273,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Mats Eriksson</t>
+          <t>Anna Zeffer</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Mats Eriksson</t>
+          <t>Anna Zeffer</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129041317</v>
+        <v>129042872</v>
       </c>
       <c r="B17" t="n">
-        <v>95963</v>
+        <v>97598</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2296,37 +2296,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2810</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Assleröd bränna, Assleröd bränna, Boh</t>
+          <t>Assleröd, Boh</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>330509</v>
+        <v>330413</v>
       </c>
       <c r="R17" t="n">
-        <v>6438703</v>
+        <v>6438980</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2380,12 +2380,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anna Zeffer</t>
+          <t>Mats Eriksson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anna Zeffer</t>
+          <t>Mats Eriksson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 34396-2023 artfynd.xlsx
+++ b/artfynd/A 34396-2023 artfynd.xlsx
@@ -2609,7 +2609,7 @@
         <v>129128187</v>
       </c>
       <c r="B20" t="n">
-        <v>97598</v>
+        <v>97627</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 34396-2023 artfynd.xlsx
+++ b/artfynd/A 34396-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2714,6 +2714,113 @@
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>131467465</v>
+      </c>
+      <c r="B21" t="n">
+        <v>97887</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Assleröd , Assleröd , Boh</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>330275</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6438726</v>
+      </c>
+      <c r="S21" t="n">
+        <v>11</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Västerlanda</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Anna Zeffer</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Anna Zeffer</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34396-2023 artfynd.xlsx
+++ b/artfynd/A 34396-2023 artfynd.xlsx
@@ -2719,7 +2719,7 @@
         <v>131467465</v>
       </c>
       <c r="B21" t="n">
-        <v>97887</v>
+        <v>97888</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 34396-2023 artfynd.xlsx
+++ b/artfynd/A 34396-2023 artfynd.xlsx
@@ -2719,7 +2719,7 @@
         <v>131467465</v>
       </c>
       <c r="B21" t="n">
-        <v>97888</v>
+        <v>97891</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 34396-2023 artfynd.xlsx
+++ b/artfynd/A 34396-2023 artfynd.xlsx
@@ -2719,7 +2719,7 @@
         <v>131467465</v>
       </c>
       <c r="B21" t="n">
-        <v>97891</v>
+        <v>97892</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 34396-2023 artfynd.xlsx
+++ b/artfynd/A 34396-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128916103</v>
+        <v>129188673</v>
       </c>
       <c r="B2" t="n">
-        <v>97587</v>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Assleröd bränna, Boh</t>
+          <t>Assleröd , Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>330449</v>
+        <v>330401</v>
       </c>
       <c r="R2" t="n">
-        <v>6438727</v>
+        <v>6439091</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,22 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:32</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:32</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,28 +758,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Anna Zeffer</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Anna Zeffer</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128916024</v>
+        <v>129041453</v>
       </c>
       <c r="B3" t="n">
-        <v>97793</v>
+        <v>97733</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,37 +788,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220686</v>
+        <v>2569</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Assleröd bränna, Boh</t>
+          <t>Assleröd bränna, Assleröd bränna, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>330449</v>
+        <v>330531</v>
       </c>
       <c r="R3" t="n">
-        <v>6438727</v>
+        <v>6438749</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,22 +842,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:31</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:31</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,22 +862,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128916540</v>
+        <v>128915036</v>
       </c>
       <c r="B4" t="n">
-        <v>97587</v>
+        <v>96348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>2810</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,13 +909,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>330284</v>
+        <v>330473</v>
       </c>
       <c r="R4" t="n">
-        <v>6438742</v>
+        <v>6438664</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -959,7 +944,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +954,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,7 +984,7 @@
         <v>128916877</v>
       </c>
       <c r="B5" t="n">
-        <v>95952</v>
+        <v>96348</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128915303</v>
+        <v>129041317</v>
       </c>
       <c r="B6" t="n">
-        <v>97793</v>
+        <v>96348</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,37 +1099,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220686</v>
+        <v>2810</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Assleröd bränna, Boh</t>
+          <t>Assleröd bränna, Assleröd bränna, Boh</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>330473</v>
+        <v>330509</v>
       </c>
       <c r="R6" t="n">
-        <v>6438664</v>
+        <v>6438703</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1168,22 +1153,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-11</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-11</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1198,22 +1183,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Anna Zeffer</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Anna Zeffer</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128915345</v>
+        <v>129043852</v>
       </c>
       <c r="B7" t="n">
-        <v>97587</v>
+        <v>96348</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,34 +1206,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>2810</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Assleröd bränna, Boh</t>
+          <t>Assleröd, Assleröd, Boh</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>330474</v>
+        <v>330381</v>
       </c>
       <c r="R7" t="n">
-        <v>6438708</v>
+        <v>6439100</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1275,22 +1260,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-11</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-11</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128915036</v>
+        <v>129045313</v>
       </c>
       <c r="B8" t="n">
-        <v>95952</v>
+        <v>96348</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1348,17 +1333,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Assleröd bränna, Boh</t>
+          <t>Assleröd bränna, Assleröd bränna, Boh</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>330473</v>
+        <v>330360</v>
       </c>
       <c r="R8" t="n">
-        <v>6438664</v>
+        <v>6438739</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1382,22 +1367,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-11</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-11</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1412,26 +1397,26 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Anna Zeffer</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Anna Zeffer</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129042968</v>
+        <v>128917810</v>
       </c>
       <c r="B9" t="n">
-        <v>57724</v>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1459,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>330366</v>
+        <v>330141</v>
       </c>
       <c r="R9" t="n">
-        <v>6438992</v>
+        <v>6438880</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1489,22 +1474,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1519,22 +1504,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anna Zeffer</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anna Zeffer</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129045442</v>
+        <v>129041609</v>
       </c>
       <c r="B10" t="n">
-        <v>8439</v>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1542,21 +1527,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>330427</v>
+        <v>330531</v>
       </c>
       <c r="R10" t="n">
-        <v>6438678</v>
+        <v>6438749</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1586,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,7 +1596,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Medelfärskt spår av födosökande spillkråka på låga</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1626,12 +1616,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anna Zeffer</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anna Zeffer</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1641,11 +1631,11 @@
         <v>129041729</v>
       </c>
       <c r="B11" t="n">
-        <v>57724</v>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1745,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129044975</v>
+        <v>129042968</v>
       </c>
       <c r="B12" t="n">
-        <v>97598</v>
+        <v>57950</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>330281</v>
+        <v>330366</v>
       </c>
       <c r="R12" t="n">
-        <v>6438766</v>
+        <v>6438992</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1805,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1815,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,10 +1842,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129041254</v>
+        <v>129043672</v>
       </c>
       <c r="B13" t="n">
-        <v>97804</v>
+        <v>57950</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,37 +1853,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220686</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Assleröd bränna, Assleröd bränna, Boh</t>
+          <t>Assleröd, Boh</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>330526</v>
+        <v>330384</v>
       </c>
       <c r="R13" t="n">
-        <v>6438666</v>
+        <v>6439117</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1922,7 +1912,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1922,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1947,60 +1942,60 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anna Zeffer</t>
+          <t>Mats Eriksson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anna Zeffer</t>
+          <t>Mats Eriksson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129043672</v>
+        <v>129045442</v>
       </c>
       <c r="B14" t="n">
-        <v>57724</v>
+        <v>8444</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Assleröd, Boh</t>
+          <t>Assleröd bränna, Assleröd bränna, Boh</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>330384</v>
+        <v>330427</v>
       </c>
       <c r="R14" t="n">
-        <v>6439117</v>
+        <v>6438678</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2029,7 +2024,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,12 +2034,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:20</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Hack</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2059,22 +2049,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Mats Eriksson</t>
+          <t>Anna Zeffer</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Mats Eriksson</t>
+          <t>Anna Zeffer</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129043852</v>
+        <v>128915303</v>
       </c>
       <c r="B15" t="n">
-        <v>95963</v>
+        <v>98194</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2082,37 +2072,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2810</v>
+        <v>220686</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Assleröd, Assleröd, Boh</t>
+          <t>Assleröd bränna, Boh</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>330381</v>
+        <v>330473</v>
       </c>
       <c r="R15" t="n">
-        <v>6439100</v>
+        <v>6438664</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2136,22 +2126,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2178,10 +2168,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129041317</v>
+        <v>128916024</v>
       </c>
       <c r="B16" t="n">
-        <v>95963</v>
+        <v>98194</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2189,37 +2179,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2810</v>
+        <v>220686</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Assleröd bränna, Assleröd bränna, Boh</t>
+          <t>Assleröd bränna, Boh</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>330509</v>
+        <v>330449</v>
       </c>
       <c r="R16" t="n">
-        <v>6438703</v>
+        <v>6438727</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2243,22 +2233,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2273,22 +2263,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anna Zeffer</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anna Zeffer</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129042872</v>
+        <v>129041254</v>
       </c>
       <c r="B17" t="n">
-        <v>97598</v>
+        <v>98194</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2296,37 +2286,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>220686</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Assleröd, Boh</t>
+          <t>Assleröd bränna, Assleröd bränna, Boh</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>330413</v>
+        <v>330526</v>
       </c>
       <c r="R17" t="n">
-        <v>6438980</v>
+        <v>6438666</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2355,7 +2345,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2365,7 +2355,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2380,22 +2370,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Mats Eriksson</t>
+          <t>Anna Zeffer</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Mats Eriksson</t>
+          <t>Anna Zeffer</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129045313</v>
+        <v>129045237</v>
       </c>
       <c r="B18" t="n">
-        <v>95963</v>
+        <v>98194</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2403,21 +2393,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2810</v>
+        <v>220686</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2462,7 +2452,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2472,7 +2462,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2499,10 +2489,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129045237</v>
+        <v>128915345</v>
       </c>
       <c r="B19" t="n">
-        <v>97804</v>
+        <v>97983</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2510,34 +2500,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220686</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Assleröd bränna, Assleröd bränna, Boh</t>
+          <t>Assleröd bränna, Boh</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>330360</v>
+        <v>330474</v>
       </c>
       <c r="R19" t="n">
-        <v>6438739</v>
+        <v>6438708</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2564,22 +2554,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2594,22 +2584,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anna Zeffer</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anna Zeffer</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129128187</v>
+        <v>128916103</v>
       </c>
       <c r="B20" t="n">
-        <v>97627</v>
+        <v>97983</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2634,29 +2624,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Assleröd, Boh</t>
+          <t>Assleröd bränna, Boh</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>330393</v>
+        <v>330449</v>
       </c>
       <c r="R20" t="n">
-        <v>6439061</v>
+        <v>6438727</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2683,12 +2661,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2697,29 +2685,28 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anna Zeffer</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anna Zeffer</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131467465</v>
+        <v>128916540</v>
       </c>
       <c r="B21" t="n">
-        <v>97919</v>
+        <v>97983</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2747,17 +2734,17 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Assleröd , Assleröd , Boh</t>
+          <t>Assleröd bränna, Boh</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>330275</v>
+        <v>330284</v>
       </c>
       <c r="R21" t="n">
-        <v>6438726</v>
+        <v>6438742</v>
       </c>
       <c r="S21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2781,22 +2768,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2811,15 +2798,456 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129042872</v>
+      </c>
+      <c r="B22" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Assleröd, Boh</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>330413</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6438980</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Västerlanda</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Mats Eriksson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Mats Eriksson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129043878</v>
+      </c>
+      <c r="B23" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Assleröd, Boh</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>330393</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6439061</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Västerlanda</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Mats Eriksson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Mats Eriksson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129044975</v>
+      </c>
+      <c r="B24" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Assleröd bränna, Assleröd bränna, Boh</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>330281</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6438766</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Västerlanda</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
           <t>Anna Zeffer</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
+      <c r="AX24" t="inlineStr">
         <is>
           <t>Anna Zeffer</t>
         </is>
       </c>
-      <c r="AY21" t="inlineStr"/>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>131467465</v>
+      </c>
+      <c r="B25" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Assleröd , Assleröd , Boh</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>330275</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6438726</v>
+      </c>
+      <c r="S25" t="n">
+        <v>11</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Västerlanda</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Anna Zeffer</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Anna Zeffer</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34396-2023 artfynd.xlsx
+++ b/artfynd/A 34396-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129188673</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129041453</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128915036</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1085,6 +1105,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128916877</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1192,6 +1217,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129041317</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1299,6 +1329,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129043852</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1406,6 +1441,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129045313</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1513,6 +1553,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128917810</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1625,6 +1670,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129041609</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1732,6 +1782,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129041729</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1839,6 +1894,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129042968</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1951,6 +2011,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129043672</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2058,6 +2123,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129045442</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2165,6 +2235,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128915303</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2272,6 +2347,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128916024</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2379,6 +2459,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129041254</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2486,6 +2571,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129045237</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2593,6 +2683,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128915345</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2700,6 +2795,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128916103</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2807,6 +2907,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128916540</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2914,6 +3019,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129042872</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3034,6 +3144,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129043878</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3141,6 +3256,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129044975</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3248,8 +3368,39 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131467465</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>